--- a/results/q4_summary.xlsx
+++ b/results/q4_summary.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,12 +417,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -497,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18653937.18</v>
+        <v>15869578.32</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19025516.93</v>
+        <v>15979533.22</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.99</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>228929.35</v>
+        <v>53117.98</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1194152.8</v>
+        <v>333634.55</v>
       </c>
     </row>
   </sheetData>

--- a/results/q4_summary.xlsx
+++ b/results/q4_summary.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,12 +417,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -447,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16085410.43</v>
+        <v>16585439.75</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16244576.3</v>
+        <v>16690155.07</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.99</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>109461.66</v>
+        <v>34106.16</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>733342.71</v>
+        <v>232193.87</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18653937.18</v>
+        <v>17617108.75</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19025516.93</v>
+        <v>17834905.39</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.99</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>228929.35</v>
+        <v>94089.84</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1194152.8</v>
+        <v>541241.1</v>
       </c>
     </row>
   </sheetData>

--- a/results/q4_summary.xlsx
+++ b/results/q4_summary.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,12 +429,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -435,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16585439.75</v>
+        <v>16085410.43</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16690155.07</v>
+        <v>16244576.3</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.63</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34106.16</v>
+        <v>109461.66</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>232193.87</v>
+        <v>733342.71</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17617108.75</v>
+        <v>15867644.03</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17834905.39</v>
+        <v>16010183.96</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.24</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -515,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94089.84</v>
+        <v>44783.01</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>541241.1</v>
+        <v>273106.14</v>
       </c>
     </row>
   </sheetData>
